--- a/data/trans_orig/P36BPD11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023</t>
+          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>247247</t>
+          <t>245677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302019</t>
+          <t>300260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>299108</t>
+          <t>300158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>341015</t>
+          <t>342225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558794</t>
+          <t>557466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>629541</t>
+          <t>626753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186132</t>
+          <t>188232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239208</t>
+          <t>238774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220593</t>
+          <t>218747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262022</t>
+          <t>260750</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>421421</t>
+          <t>420289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487106</t>
+          <t>488242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>123609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174920</t>
+          <t>174320</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>98012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>130012</t>
+          <t>129590</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231769</t>
+          <t>233959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>292027</t>
+          <t>295996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>507988</t>
+          <t>508650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>901234</t>
+          <t>939435</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431703</t>
+          <t>431448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485276</t>
+          <t>485870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>973295</t>
+          <t>974530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1450141</t>
+          <t>1482915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>196278</t>
+          <t>173708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>464332</t>
+          <t>463431</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>336259</t>
+          <t>335440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>388087</t>
+          <t>388172</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>492789</t>
+          <t>464800</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>824213</t>
+          <t>819375</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88812</t>
+          <t>81654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233515</t>
+          <t>232011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119946</t>
+          <t>120177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159923</t>
+          <t>158879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201715</t>
+          <t>218356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367868</t>
+          <t>367772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>306538</t>
+          <t>306396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>368799</t>
+          <t>369857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>409781</t>
+          <t>405843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>719586</t>
+          <t>741256</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>750415</t>
+          <t>745730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1162339</t>
+          <t>1131129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>247717</t>
+          <t>248228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>308987</t>
+          <t>311159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142232</t>
+          <t>125371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>346692</t>
+          <t>350494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>332603</t>
+          <t>363534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>628318</t>
+          <t>628796</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69226</t>
+          <t>69520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112208</t>
+          <t>110228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71462</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>217793</t>
+          <t>224688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>149509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315411</t>
+          <t>311560</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>404217</t>
+          <t>405051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>468978</t>
+          <t>468624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>409702</t>
+          <t>433540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>581989</t>
+          <t>586006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>847589</t>
+          <t>847673</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1027611</t>
+          <t>1024841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300410</t>
+          <t>302767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367697</t>
+          <t>369293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364705</t>
+          <t>361378</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>579915</t>
+          <t>550496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>693968</t>
+          <t>690938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>907062</t>
+          <t>916584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134139</t>
+          <t>132714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183737</t>
+          <t>181251</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>110479</t>
+          <t>108708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162350</t>
+          <t>160942</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>260559</t>
+          <t>257074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331491</t>
+          <t>329393</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1551316</t>
+          <t>1560465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2095125</t>
+          <t>2120679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1705155</t>
+          <t>1699167</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2159875</t>
+          <t>2151185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3325296</t>
+          <t>3324335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4035101</t>
+          <t>4055399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>921631</t>
+          <t>936617</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1294714</t>
+          <t>1290988</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1077364</t>
+          <t>1065539</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1411226</t>
+          <t>1414550</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2131153</t>
+          <t>2162248</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2643408</t>
+          <t>2652470</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>441437</t>
+          <t>437713</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>636436</t>
+          <t>631582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>443238</t>
+          <t>445627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>617538</t>
+          <t>625199</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>962760</t>
+          <t>958600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1223539</t>
+          <t>1203347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>273936</t>
+          <t>307343</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>245677</t>
+          <t>280073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>300260</t>
+          <t>338846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>319684</t>
+          <t>348472</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300158</t>
+          <t>325154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>342225</t>
+          <t>369022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>593620</t>
+          <t>655816</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>557466</t>
+          <t>617372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>626753</t>
+          <t>689921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>212126</t>
+          <t>226545</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>188232</t>
+          <t>200928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238774</t>
+          <t>253377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>240917</t>
+          <t>258324</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218747</t>
+          <t>237503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260750</t>
+          <t>279721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>453043</t>
+          <t>484869</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>420289</t>
+          <t>452223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>488242</t>
+          <t>521194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -951,102 +951,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146727</t>
+          <t>152541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123609</t>
+          <t>129068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174320</t>
+          <t>179766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>124334</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>108752</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>144546</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>276875</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>247354</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>309869</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>19,53%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>113193</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98012</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>129590</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>19,23%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>259921</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>233959</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>295996</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>632789</t>
+          <t>686429</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>632789</t>
+          <t>686429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>632789</t>
+          <t>686429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>673794</t>
+          <t>731131</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>673794</t>
+          <t>731131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>673794</t>
+          <t>731131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1306583</t>
+          <t>1417560</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1306583</t>
+          <t>1417560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1306583</t>
+          <t>1417560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>660251</t>
+          <t>467105</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>508650</t>
+          <t>431227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>939435</t>
+          <t>505881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>458904</t>
+          <t>511317</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431448</t>
+          <t>480662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485870</t>
+          <t>539636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1119155</t>
+          <t>978422</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>974530</t>
+          <t>933277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1482915</t>
+          <t>1022049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>357022</t>
+          <t>388190</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173708</t>
+          <t>355228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>463431</t>
+          <t>423857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>360158</t>
+          <t>400070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>335440</t>
+          <t>370890</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>388172</t>
+          <t>428838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>717180</t>
+          <t>788259</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>464800</t>
+          <t>744941</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>819375</t>
+          <t>830667</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>175591</t>
+          <t>193622</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>167986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>232011</t>
+          <t>225449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120177</t>
+          <t>138331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158879</t>
+          <t>183555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>313555</t>
+          <t>351853</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218356</t>
+          <t>321199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367772</t>
+          <t>392741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957026</t>
+          <t>1069617</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957026</t>
+          <t>1069617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957026</t>
+          <t>1069617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149890</t>
+          <t>2118534</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149890</t>
+          <t>2118534</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149890</t>
+          <t>2118534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>338402</t>
+          <t>390209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>306396</t>
+          <t>357120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>369857</t>
+          <t>422589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533365</t>
+          <t>381467</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>405843</t>
+          <t>357225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>741256</t>
+          <t>410381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>871767</t>
+          <t>771675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>745730</t>
+          <t>730992</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1131129</t>
+          <t>821282</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>277577</t>
+          <t>303670</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>248228</t>
+          <t>273137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>311159</t>
+          <t>336122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>260427</t>
+          <t>303246</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>125371</t>
+          <t>278256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>350494</t>
+          <t>330260</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>538004</t>
+          <t>606917</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363534</t>
+          <t>564574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>628796</t>
+          <t>651009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88702</t>
+          <t>109194</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69520</t>
+          <t>88026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110228</t>
+          <t>135658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>138855</t>
+          <t>126808</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70674</t>
+          <t>107552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224688</t>
+          <t>149531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>227556</t>
+          <t>236002</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149509</t>
+          <t>204959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>311560</t>
+          <t>268157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>811521</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>811521</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>811521</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637327</t>
+          <t>1614594</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637327</t>
+          <t>1614594</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637327</t>
+          <t>1614594</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>435429</t>
+          <t>456551</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>405051</t>
+          <t>424872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>468624</t>
+          <t>488422</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>536117</t>
+          <t>578262</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>433540</t>
+          <t>547566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>586006</t>
+          <t>607211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>971546</t>
+          <t>1034813</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>847673</t>
+          <t>990079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1024841</t>
+          <t>1077882</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>335797</t>
+          <t>362906</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302767</t>
+          <t>331775</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>369293</t>
+          <t>392041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>418057</t>
+          <t>381347</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361378</t>
+          <t>354269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550496</t>
+          <t>410963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>753853</t>
+          <t>744253</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>690938</t>
+          <t>703993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916584</t>
+          <t>788417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>155605</t>
+          <t>170606</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132714</t>
+          <t>144820</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181251</t>
+          <t>196257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>138928</t>
+          <t>157463</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>137065</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160942</t>
+          <t>180715</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>294534</t>
+          <t>328069</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>257074</t>
+          <t>295831</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329393</t>
+          <t>361583</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1093102</t>
+          <t>1117072</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1093102</t>
+          <t>1117072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1093102</t>
+          <t>1117072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019933</t>
+          <t>2107134</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019933</t>
+          <t>2107134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019933</t>
+          <t>2107134</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1708017</t>
+          <t>1621208</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1560465</t>
+          <t>1552429</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2120679</t>
+          <t>1683890</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1848070</t>
+          <t>1819517</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1699167</t>
+          <t>1760876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2151185</t>
+          <t>1869046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3556088</t>
+          <t>3440725</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3324335</t>
+          <t>3358972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4055399</t>
+          <t>3518196</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1182522</t>
+          <t>1281311</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>936617</t>
+          <t>1217939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1290988</t>
+          <t>1344833</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1279558</t>
+          <t>1342987</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1065539</t>
+          <t>1289892</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1414550</t>
+          <t>1398694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2462079</t>
+          <t>2624298</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2162248</t>
+          <t>2548013</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2652470</t>
+          <t>2716157</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>566626</t>
+          <t>625963</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>437713</t>
+          <t>574518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>631582</t>
+          <t>681426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>528940</t>
+          <t>566836</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>445627</t>
+          <t>525036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>625199</t>
+          <t>606701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1095566</t>
+          <t>1192799</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>958600</t>
+          <t>1126219</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1203347</t>
+          <t>1259873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
